--- a/data/nzd0044/nzd0044.xlsx
+++ b/data/nzd0044/nzd0044.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H524"/>
+  <dimension ref="A1:H525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16158,6 +16158,36 @@
         <v>384.61</v>
       </c>
       <c r="H524" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>380.5</v>
+      </c>
+      <c r="C525" t="n">
+        <v>369.4</v>
+      </c>
+      <c r="D525" t="n">
+        <v>369.78</v>
+      </c>
+      <c r="E525" t="n">
+        <v>372.15</v>
+      </c>
+      <c r="F525" t="n">
+        <v>378.24</v>
+      </c>
+      <c r="G525" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="H525" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -16174,7 +16204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B603"/>
+  <dimension ref="A1:B604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22207,6 +22237,16 @@
       </c>
       <c r="B603" t="n">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -22375,28 +22415,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03600765380285161</v>
+        <v>-0.03732254243910074</v>
       </c>
       <c r="J2" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K2" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004180196670356295</v>
+        <v>0.004500095064334575</v>
       </c>
       <c r="M2" t="n">
-        <v>3.44179092985483</v>
+        <v>3.443487969232355</v>
       </c>
       <c r="N2" t="n">
-        <v>18.69927969382736</v>
+        <v>18.69111631268606</v>
       </c>
       <c r="O2" t="n">
-        <v>4.324266376372686</v>
+        <v>4.323322369739048</v>
       </c>
       <c r="P2" t="n">
-        <v>385.2514332558931</v>
+        <v>385.2642671915085</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22453,28 +22493,28 @@
         <v>0.111</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03679564085557926</v>
+        <v>0.03474928342991988</v>
       </c>
       <c r="J3" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K3" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005702590018341391</v>
+        <v>0.005084728625971757</v>
       </c>
       <c r="M3" t="n">
-        <v>2.939297547055275</v>
+        <v>2.94629481175744</v>
       </c>
       <c r="N3" t="n">
-        <v>14.29183804975432</v>
+        <v>14.33122415377678</v>
       </c>
       <c r="O3" t="n">
-        <v>3.780454741132913</v>
+        <v>3.785660332594141</v>
       </c>
       <c r="P3" t="n">
-        <v>374.3576162453555</v>
+        <v>374.3775896626646</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22531,28 +22571,28 @@
         <v>0.1222</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06629833621765394</v>
+        <v>-0.06859881411625036</v>
       </c>
       <c r="J4" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K4" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02629613777792617</v>
+        <v>0.02797172568480744</v>
       </c>
       <c r="M4" t="n">
-        <v>2.588837182796502</v>
+        <v>2.597912397738614</v>
       </c>
       <c r="N4" t="n">
-        <v>9.853519282005317</v>
+        <v>9.918959517876972</v>
       </c>
       <c r="O4" t="n">
-        <v>3.139031583467315</v>
+        <v>3.149437968571055</v>
       </c>
       <c r="P4" t="n">
-        <v>378.1822090027332</v>
+        <v>378.20466275617</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22609,28 +22649,28 @@
         <v>0.1361</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1371285724809596</v>
+        <v>-0.1394491297744432</v>
       </c>
       <c r="J5" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K5" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1049280609481579</v>
+        <v>0.1076407728715082</v>
       </c>
       <c r="M5" t="n">
-        <v>2.432711131368343</v>
+        <v>2.440835205918373</v>
       </c>
       <c r="N5" t="n">
-        <v>9.711210990218976</v>
+        <v>9.778399860069927</v>
       </c>
       <c r="O5" t="n">
-        <v>3.116281596746189</v>
+        <v>3.127043309592934</v>
       </c>
       <c r="P5" t="n">
-        <v>382.4769728318992</v>
+        <v>382.4996225697364</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22687,28 +22727,28 @@
         <v>0.1034</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09968065674429825</v>
+        <v>-0.1018526186791645</v>
       </c>
       <c r="J6" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K6" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02265572606678246</v>
+        <v>0.02365115649091987</v>
       </c>
       <c r="M6" t="n">
-        <v>4.165987672426415</v>
+        <v>4.171670926839068</v>
       </c>
       <c r="N6" t="n">
-        <v>25.95031024979762</v>
+        <v>25.97588169805574</v>
       </c>
       <c r="O6" t="n">
-        <v>5.094144702479271</v>
+        <v>5.096653970798464</v>
       </c>
       <c r="P6" t="n">
-        <v>387.1526432507154</v>
+        <v>387.1738426275011</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22765,28 +22805,28 @@
         <v>0.1285</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2148142698665256</v>
+        <v>-0.2173462323422918</v>
       </c>
       <c r="J7" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K7" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07671215997204262</v>
+        <v>0.07844401897965425</v>
       </c>
       <c r="M7" t="n">
-        <v>4.601715866380986</v>
+        <v>4.608732527062654</v>
       </c>
       <c r="N7" t="n">
-        <v>33.62407494908248</v>
+        <v>33.66195869590756</v>
       </c>
       <c r="O7" t="n">
-        <v>5.798626988269075</v>
+        <v>5.801892682212207</v>
       </c>
       <c r="P7" t="n">
-        <v>397.57992823654</v>
+        <v>397.6046413890447</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22824,7 +22864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H524"/>
+  <dimension ref="A1:H525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44835,6 +44875,48 @@
         </is>
       </c>
     </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-35.00170516974845,173.7913353182704</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-35.00190924047812,173.79220655762245</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>-35.00198612455297,173.79309422512344</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>-35.00197088406257,173.7939813766348</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>-35.00183661128046,173.79484445176354</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>-35.00156574830775,173.79564340782002</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0044/nzd0044.xlsx
+++ b/data/nzd0044/nzd0044.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H525"/>
+  <dimension ref="A1:H527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16190,6 +16190,66 @@
       <c r="H525" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>379.53</v>
+      </c>
+      <c r="C526" t="n">
+        <v>368.83</v>
+      </c>
+      <c r="D526" t="n">
+        <v>370.02</v>
+      </c>
+      <c r="E526" t="n">
+        <v>372.25</v>
+      </c>
+      <c r="F526" t="n">
+        <v>379.03</v>
+      </c>
+      <c r="G526" t="n">
+        <v>385.86</v>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>378.61</v>
+      </c>
+      <c r="C527" t="n">
+        <v>368.2</v>
+      </c>
+      <c r="D527" t="n">
+        <v>369.73</v>
+      </c>
+      <c r="E527" t="n">
+        <v>371.89</v>
+      </c>
+      <c r="F527" t="n">
+        <v>378.15</v>
+      </c>
+      <c r="G527" t="n">
+        <v>385.93</v>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16204,7 +16264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B604"/>
+  <dimension ref="A1:B606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22247,6 +22307,26 @@
       </c>
       <c r="B604" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -22415,28 +22495,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03732254243910074</v>
+        <v>-0.04089960493441461</v>
       </c>
       <c r="J2" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K2" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004500095064334575</v>
+        <v>0.005410328269119802</v>
       </c>
       <c r="M2" t="n">
-        <v>3.443487969232355</v>
+        <v>3.452866516860842</v>
       </c>
       <c r="N2" t="n">
-        <v>18.69111631268606</v>
+        <v>18.72301916149561</v>
       </c>
       <c r="O2" t="n">
-        <v>4.323322369739048</v>
+        <v>4.327010418463955</v>
       </c>
       <c r="P2" t="n">
-        <v>385.2642671915085</v>
+        <v>385.2992809310071</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22493,28 +22573,28 @@
         <v>0.111</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03474928342991988</v>
+        <v>0.03009779801753823</v>
       </c>
       <c r="J3" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K3" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005084728625971757</v>
+        <v>0.003802486718817111</v>
       </c>
       <c r="M3" t="n">
-        <v>2.94629481175744</v>
+        <v>2.963737410789184</v>
       </c>
       <c r="N3" t="n">
-        <v>14.33122415377678</v>
+        <v>14.44988934956511</v>
       </c>
       <c r="O3" t="n">
-        <v>3.785660332594141</v>
+        <v>3.801301007492712</v>
       </c>
       <c r="P3" t="n">
-        <v>374.3775896626646</v>
+        <v>374.4231192259579</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22571,28 +22651,28 @@
         <v>0.1222</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06859881411625036</v>
+        <v>-0.0730746470620519</v>
       </c>
       <c r="J4" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K4" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02797172568480744</v>
+        <v>0.0313633030884134</v>
       </c>
       <c r="M4" t="n">
-        <v>2.597912397738614</v>
+        <v>2.61552834607625</v>
       </c>
       <c r="N4" t="n">
-        <v>9.918959517876972</v>
+        <v>10.041299098213</v>
       </c>
       <c r="O4" t="n">
-        <v>3.149437968571055</v>
+        <v>3.16880089280046</v>
       </c>
       <c r="P4" t="n">
-        <v>378.20466275617</v>
+        <v>378.2484723783552</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22649,28 +22729,28 @@
         <v>0.1361</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1394491297744432</v>
+        <v>-0.1440853822339509</v>
       </c>
       <c r="J5" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K5" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1076407728715082</v>
+        <v>0.1130918025992551</v>
       </c>
       <c r="M5" t="n">
-        <v>2.440835205918373</v>
+        <v>2.45729262743783</v>
       </c>
       <c r="N5" t="n">
-        <v>9.778399860069927</v>
+        <v>9.912991086763819</v>
       </c>
       <c r="O5" t="n">
-        <v>3.127043309592934</v>
+        <v>3.148490286909556</v>
       </c>
       <c r="P5" t="n">
-        <v>382.4996225697364</v>
+        <v>382.5450025073597</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22727,28 +22807,28 @@
         <v>0.1034</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1018526186791645</v>
+        <v>-0.105903399389422</v>
       </c>
       <c r="J6" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K6" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02365115649091987</v>
+        <v>0.02558353235261368</v>
       </c>
       <c r="M6" t="n">
-        <v>4.171670926839068</v>
+        <v>4.181410360983377</v>
       </c>
       <c r="N6" t="n">
-        <v>25.97588169805574</v>
+        <v>26.008855137525</v>
       </c>
       <c r="O6" t="n">
-        <v>5.096653970798464</v>
+        <v>5.099887757345744</v>
       </c>
       <c r="P6" t="n">
-        <v>387.1738426275011</v>
+        <v>387.2134929856631</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22805,28 +22885,28 @@
         <v>0.1285</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2173462323422918</v>
+        <v>-0.2214575786997671</v>
       </c>
       <c r="J7" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K7" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07844401897965425</v>
+        <v>0.08146385039650361</v>
       </c>
       <c r="M7" t="n">
-        <v>4.608732527062654</v>
+        <v>4.616648101387966</v>
       </c>
       <c r="N7" t="n">
-        <v>33.66195869590756</v>
+        <v>33.66896308774881</v>
       </c>
       <c r="O7" t="n">
-        <v>5.801892682212207</v>
+        <v>5.802496280718223</v>
       </c>
       <c r="P7" t="n">
-        <v>397.6046413890447</v>
+        <v>397.6448827708294</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22864,7 +22944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H525"/>
+  <dimension ref="A1:H527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44917,6 +44997,90 @@
         </is>
       </c>
     </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>-35.00171383254531,173.79133385250404</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>-35.001914342144474,173.79220580004517</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>-35.001983963640136,173.7930943665851</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>-35.00196998388649,173.7939813132546</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>-35.001829654398136,173.79484259135174</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>-35.00155495308815,173.79563910405435</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>-35.00172204880624,173.79133246229233</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>-35.00191998082833,173.7922049627228</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>-35.001986574743135,173.7930941956523</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>-35.00197322452039,173.79398154142336</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>-35.00183740383665,173.79484466370923</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>-35.001554353353725,173.79563886495632</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0044/nzd0044.xlsx
+++ b/data/nzd0044/nzd0044.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H527"/>
+  <dimension ref="A1:H530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16248,6 +16248,96 @@
         <v>385.93</v>
       </c>
       <c r="H527" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>376.84</v>
+      </c>
+      <c r="C528" t="n">
+        <v>366.33</v>
+      </c>
+      <c r="D528" t="n">
+        <v>368.44</v>
+      </c>
+      <c r="E528" t="n">
+        <v>370.67</v>
+      </c>
+      <c r="F528" t="n">
+        <v>375.71</v>
+      </c>
+      <c r="G528" t="n">
+        <v>385.06</v>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>376.06</v>
+      </c>
+      <c r="C529" t="n">
+        <v>366.1</v>
+      </c>
+      <c r="D529" t="n">
+        <v>368.28</v>
+      </c>
+      <c r="E529" t="n">
+        <v>370.67</v>
+      </c>
+      <c r="F529" t="n">
+        <v>375.71</v>
+      </c>
+      <c r="G529" t="n">
+        <v>385.06</v>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>376.76</v>
+      </c>
+      <c r="C530" t="n">
+        <v>366.89</v>
+      </c>
+      <c r="D530" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="E530" t="n">
+        <v>371.35</v>
+      </c>
+      <c r="F530" t="n">
+        <v>377.11</v>
+      </c>
+      <c r="G530" t="n">
+        <v>386.24</v>
+      </c>
+      <c r="H530" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16264,7 +16354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B606"/>
+  <dimension ref="A1:B609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22327,6 +22417,36 @@
       </c>
       <c r="B606" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>
@@ -22495,28 +22615,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04089960493441461</v>
+        <v>-0.04870469082231284</v>
       </c>
       <c r="J2" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="K2" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005410328269119802</v>
+        <v>0.007608382614427089</v>
       </c>
       <c r="M2" t="n">
-        <v>3.452866516860842</v>
+        <v>3.482436553288321</v>
       </c>
       <c r="N2" t="n">
-        <v>18.72301916149561</v>
+        <v>18.94509948610239</v>
       </c>
       <c r="O2" t="n">
-        <v>4.327010418463955</v>
+        <v>4.352596866940745</v>
       </c>
       <c r="P2" t="n">
-        <v>385.2992809310071</v>
+        <v>385.3759523664765</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22573,28 +22693,28 @@
         <v>0.111</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03009779801753823</v>
+        <v>0.0211630103442776</v>
       </c>
       <c r="J3" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="K3" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003802486718817111</v>
+        <v>0.001849764225499873</v>
       </c>
       <c r="M3" t="n">
-        <v>2.963737410789184</v>
+        <v>3.001513390925557</v>
       </c>
       <c r="N3" t="n">
-        <v>14.44988934956511</v>
+        <v>14.79786265654495</v>
       </c>
       <c r="O3" t="n">
-        <v>3.801301007492712</v>
+        <v>3.846799014316312</v>
       </c>
       <c r="P3" t="n">
-        <v>374.4231192259579</v>
+        <v>374.5108862827223</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22651,28 +22771,28 @@
         <v>0.1222</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0730746470620519</v>
+        <v>-0.08097162720974939</v>
       </c>
       <c r="J4" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="K4" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0313633030884134</v>
+        <v>0.0374427425048437</v>
       </c>
       <c r="M4" t="n">
-        <v>2.61552834607625</v>
+        <v>2.650294542206382</v>
       </c>
       <c r="N4" t="n">
-        <v>10.041299098213</v>
+        <v>10.3202263233846</v>
       </c>
       <c r="O4" t="n">
-        <v>3.16880089280046</v>
+        <v>3.212510906344849</v>
       </c>
       <c r="P4" t="n">
-        <v>378.2484723783552</v>
+        <v>378.3260448529718</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22729,28 +22849,28 @@
         <v>0.1361</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1440853822339509</v>
+        <v>-0.1520765486378671</v>
       </c>
       <c r="J5" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="K5" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1130918025992551</v>
+        <v>0.1218989452451774</v>
       </c>
       <c r="M5" t="n">
-        <v>2.45729262743783</v>
+        <v>2.4890837261043</v>
       </c>
       <c r="N5" t="n">
-        <v>9.912991086763819</v>
+        <v>10.20078542890579</v>
       </c>
       <c r="O5" t="n">
-        <v>3.148490286909556</v>
+        <v>3.193866845832148</v>
       </c>
       <c r="P5" t="n">
-        <v>382.5450025073597</v>
+        <v>382.6234997724837</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22807,28 +22927,28 @@
         <v>0.1034</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.105903399389422</v>
+        <v>-0.1142968700483429</v>
       </c>
       <c r="J6" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="K6" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02558353235261368</v>
+        <v>0.02957907477529886</v>
       </c>
       <c r="M6" t="n">
-        <v>4.181410360983377</v>
+        <v>4.210468717236288</v>
       </c>
       <c r="N6" t="n">
-        <v>26.008855137525</v>
+        <v>26.24271770388328</v>
       </c>
       <c r="O6" t="n">
-        <v>5.099887757345744</v>
+        <v>5.122764654352499</v>
       </c>
       <c r="P6" t="n">
-        <v>387.2134929856631</v>
+        <v>387.2959410232745</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22885,28 +23005,28 @@
         <v>0.1285</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2214575786997671</v>
+        <v>-0.2279233896537254</v>
       </c>
       <c r="J7" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="K7" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08146385039650361</v>
+        <v>0.08623567182927783</v>
       </c>
       <c r="M7" t="n">
-        <v>4.616648101387966</v>
+        <v>4.630065992923621</v>
       </c>
       <c r="N7" t="n">
-        <v>33.66896308774881</v>
+        <v>33.70463317815124</v>
       </c>
       <c r="O7" t="n">
-        <v>5.802496280718223</v>
+        <v>5.805569151956701</v>
       </c>
       <c r="P7" t="n">
-        <v>397.6448827708294</v>
+        <v>397.7083954721434</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22944,7 +23064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H527"/>
+  <dimension ref="A1:H530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45081,6 +45201,132 @@
         </is>
       </c>
     </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>-35.00173785617775,173.79132978764522</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>-35.001936717874,173.79220247733673</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>-35.00199818964956,173.79309343529573</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>-35.00198420666865,173.79398231466223</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>-35.001858890915955,173.7948504097934</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>-35.00156180719585,173.79564183660386</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>-35.00174482213804,173.79132860898684</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>-35.001938776441115,173.79220217164746</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>-35.001999630258105,173.79309334098792</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>-35.00198420666865,173.79398231466223</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>-35.001858890915955,173.7948504097934</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>-35.00156180719585,173.79564183660386</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>-35.001738570635204,173.79132966675718</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>-35.0019317057106,173.79220322162357</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>-35.001993327595706,173.79309375358454</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>-35.00197808547127,173.7939818836766</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>-35.00184656226396,173.7948471128595</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>-35.00155169738697,173.7956378060935</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0044/nzd0044.xlsx
+++ b/data/nzd0044/nzd0044.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H530"/>
+  <dimension ref="A1:H533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16338,6 +16338,96 @@
         <v>386.24</v>
       </c>
       <c r="H530" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>374.79</v>
+      </c>
+      <c r="C531" t="n">
+        <v>366.91</v>
+      </c>
+      <c r="D531" t="n">
+        <v>369.09</v>
+      </c>
+      <c r="E531" t="n">
+        <v>371.01</v>
+      </c>
+      <c r="F531" t="n">
+        <v>374.11</v>
+      </c>
+      <c r="G531" t="n">
+        <v>385.86</v>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>375.71</v>
+      </c>
+      <c r="C532" t="n">
+        <v>368.06</v>
+      </c>
+      <c r="D532" t="n">
+        <v>369.71</v>
+      </c>
+      <c r="E532" t="n">
+        <v>370.91</v>
+      </c>
+      <c r="F532" t="n">
+        <v>373.87</v>
+      </c>
+      <c r="G532" t="n">
+        <v>385.9</v>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>375.69</v>
+      </c>
+      <c r="C533" t="n">
+        <v>368.53</v>
+      </c>
+      <c r="D533" t="n">
+        <v>370.24</v>
+      </c>
+      <c r="E533" t="n">
+        <v>370.17</v>
+      </c>
+      <c r="F533" t="n">
+        <v>373.26</v>
+      </c>
+      <c r="G533" t="n">
+        <v>384.83</v>
+      </c>
+      <c r="H533" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16354,7 +16444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B609"/>
+  <dimension ref="A1:B612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22447,6 +22537,36 @@
       </c>
       <c r="B609" t="n">
         <v>0.62</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -22615,28 +22735,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04870469082231284</v>
+        <v>-0.0576015659825382</v>
       </c>
       <c r="J2" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="K2" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007608382614427089</v>
+        <v>0.01050118234495834</v>
       </c>
       <c r="M2" t="n">
-        <v>3.482436553288321</v>
+        <v>3.51835473430336</v>
       </c>
       <c r="N2" t="n">
-        <v>18.94509948610239</v>
+        <v>19.25720040724134</v>
       </c>
       <c r="O2" t="n">
-        <v>4.352596866940745</v>
+        <v>4.388302679538109</v>
       </c>
       <c r="P2" t="n">
-        <v>385.3759523664765</v>
+        <v>385.4644988535192</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22693,28 +22813,28 @@
         <v>0.111</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0211630103442776</v>
+        <v>0.01374253706603848</v>
       </c>
       <c r="J3" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="K3" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001849764225499873</v>
+        <v>0.0007745119964792657</v>
       </c>
       <c r="M3" t="n">
-        <v>3.001513390925557</v>
+        <v>3.02938008834928</v>
       </c>
       <c r="N3" t="n">
-        <v>14.79786265654495</v>
+        <v>15.00778770197931</v>
       </c>
       <c r="O3" t="n">
-        <v>3.846799014316312</v>
+        <v>3.873988603749282</v>
       </c>
       <c r="P3" t="n">
-        <v>374.5108862827223</v>
+        <v>374.5847341568235</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22771,28 +22891,28 @@
         <v>0.1222</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08097162720974939</v>
+        <v>-0.0876184532774678</v>
       </c>
       <c r="J4" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="K4" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0374427425048437</v>
+        <v>0.04310762532479262</v>
       </c>
       <c r="M4" t="n">
-        <v>2.650294542206382</v>
+        <v>2.677381073958365</v>
       </c>
       <c r="N4" t="n">
-        <v>10.3202263233846</v>
+        <v>10.49657584383579</v>
       </c>
       <c r="O4" t="n">
-        <v>3.212510906344849</v>
+        <v>3.239841947354189</v>
       </c>
       <c r="P4" t="n">
-        <v>378.3260448529718</v>
+        <v>378.3921954319261</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22849,28 +22969,28 @@
         <v>0.1361</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1520765486378671</v>
+        <v>-0.1601482663034355</v>
       </c>
       <c r="J5" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="K5" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1218989452451774</v>
+        <v>0.1309092990642872</v>
       </c>
       <c r="M5" t="n">
-        <v>2.4890837261043</v>
+        <v>2.521223768391743</v>
       </c>
       <c r="N5" t="n">
-        <v>10.20078542890579</v>
+        <v>10.48785266915117</v>
       </c>
       <c r="O5" t="n">
-        <v>3.193866845832148</v>
+        <v>3.238495432936594</v>
       </c>
       <c r="P5" t="n">
-        <v>382.6234997724837</v>
+        <v>382.7038431163685</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22927,28 +23047,28 @@
         <v>0.1034</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1142968700483429</v>
+        <v>-0.1250629681964508</v>
       </c>
       <c r="J6" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="K6" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02957907477529886</v>
+        <v>0.03481668048988951</v>
       </c>
       <c r="M6" t="n">
-        <v>4.210468717236288</v>
+        <v>4.254181875100457</v>
       </c>
       <c r="N6" t="n">
-        <v>26.24271770388328</v>
+        <v>26.70714095735381</v>
       </c>
       <c r="O6" t="n">
-        <v>5.122764654352499</v>
+        <v>5.167895215399962</v>
       </c>
       <c r="P6" t="n">
-        <v>387.2959410232745</v>
+        <v>387.4031023583005</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23005,28 +23125,28 @@
         <v>0.1285</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2279233896537254</v>
+        <v>-0.2341815176607303</v>
       </c>
       <c r="J7" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="K7" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08623567182927783</v>
+        <v>0.0910484588537398</v>
       </c>
       <c r="M7" t="n">
-        <v>4.630065992923621</v>
+        <v>4.641704104572937</v>
       </c>
       <c r="N7" t="n">
-        <v>33.70463317815124</v>
+        <v>33.72258460234907</v>
       </c>
       <c r="O7" t="n">
-        <v>5.805569151956701</v>
+        <v>5.807114998202556</v>
       </c>
       <c r="P7" t="n">
-        <v>397.7083954721434</v>
+        <v>397.7706885193282</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23064,7 +23184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H530"/>
+  <dimension ref="A1:H533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45327,6 +45447,132 @@
         </is>
       </c>
     </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>-35.00175616415029,173.79132668988885</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>-35.00193152670475,173.79220324820523</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>-35.001992337177334,173.79309381842114</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>-35.00198114606997,173.79398209916943</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>-35.0018729808038,173.79485417771915</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>-35.00155495308815,173.79563910405435</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>-35.00174794788944,173.7913280801016</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>-35.00192123386919,173.79220477665115</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>-35.00198675481921,173.7930941838638</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>-35.00198204624605,173.79398216254964</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>-35.001875094286966,173.79485474290811</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>-35.00155461038277,173.7956389674269</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>-35.00174812650381,173.7913280498796</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>-35.001917027232025,173.79220540132025</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>-35.001981982803386,173.7930944962583</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>-35.00198870754909,173.79398263156347</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>-35.001880466056654,173.79485617943024</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>-35.0015637777518,173.79564262221194</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0044/nzd0044.xlsx
+++ b/data/nzd0044/nzd0044.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H533"/>
+  <dimension ref="A1:H536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16428,6 +16428,96 @@
         <v>384.83</v>
       </c>
       <c r="H533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>376.57</v>
+      </c>
+      <c r="C534" t="n">
+        <v>368.97</v>
+      </c>
+      <c r="D534" t="n">
+        <v>370.49</v>
+      </c>
+      <c r="E534" t="n">
+        <v>370.6</v>
+      </c>
+      <c r="F534" t="n">
+        <v>373.45</v>
+      </c>
+      <c r="G534" t="n">
+        <v>384.69</v>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>377.91</v>
+      </c>
+      <c r="C535" t="n">
+        <v>370.06</v>
+      </c>
+      <c r="D535" t="n">
+        <v>371.27</v>
+      </c>
+      <c r="E535" t="n">
+        <v>370.62</v>
+      </c>
+      <c r="F535" t="n">
+        <v>373.09</v>
+      </c>
+      <c r="G535" t="n">
+        <v>383.92</v>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>379.17</v>
+      </c>
+      <c r="C536" t="n">
+        <v>370.91</v>
+      </c>
+      <c r="D536" t="n">
+        <v>372.65</v>
+      </c>
+      <c r="E536" t="n">
+        <v>370.96</v>
+      </c>
+      <c r="F536" t="n">
+        <v>373.41</v>
+      </c>
+      <c r="G536" t="n">
+        <v>384.57</v>
+      </c>
+      <c r="H536" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16444,7 +16534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B612"/>
+  <dimension ref="A1:B615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22567,6 +22657,36 @@
       </c>
       <c r="B612" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -22735,28 +22855,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0576015659825382</v>
+        <v>-0.06372813896226034</v>
       </c>
       <c r="J2" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K2" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01050118234495834</v>
+        <v>0.0128325441592847</v>
       </c>
       <c r="M2" t="n">
-        <v>3.51835473430336</v>
+        <v>3.537580283525133</v>
       </c>
       <c r="N2" t="n">
-        <v>19.25720040724134</v>
+        <v>19.35692199808771</v>
       </c>
       <c r="O2" t="n">
-        <v>4.388302679538109</v>
+        <v>4.399650213151917</v>
       </c>
       <c r="P2" t="n">
-        <v>385.4644988535192</v>
+        <v>385.5256888077581</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22813,28 +22933,28 @@
         <v>0.111</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01374253706603848</v>
+        <v>0.008702094867847086</v>
       </c>
       <c r="J3" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K3" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007745119964792657</v>
+        <v>0.000311374418986432</v>
       </c>
       <c r="M3" t="n">
-        <v>3.02938008834928</v>
+        <v>3.043025551856806</v>
       </c>
       <c r="N3" t="n">
-        <v>15.00778770197931</v>
+        <v>15.06347647405182</v>
       </c>
       <c r="O3" t="n">
-        <v>3.873988603749282</v>
+        <v>3.881169472472417</v>
       </c>
       <c r="P3" t="n">
-        <v>374.5847341568235</v>
+        <v>374.6350769876991</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22891,28 +23011,28 @@
         <v>0.1222</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0876184532774678</v>
+        <v>-0.09225937960253983</v>
       </c>
       <c r="J4" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K4" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04310762532479262</v>
+        <v>0.04757480176365281</v>
       </c>
       <c r="M4" t="n">
-        <v>2.677381073958365</v>
+        <v>2.691788450878893</v>
       </c>
       <c r="N4" t="n">
-        <v>10.49657584383579</v>
+        <v>10.55773398549565</v>
       </c>
       <c r="O4" t="n">
-        <v>3.239841947354189</v>
+        <v>3.24926668426826</v>
       </c>
       <c r="P4" t="n">
-        <v>378.3921954319261</v>
+        <v>378.4385466268116</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22969,28 +23089,28 @@
         <v>0.1361</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1601482663034355</v>
+        <v>-0.1679550601337838</v>
       </c>
       <c r="J5" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K5" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1309092990642872</v>
+        <v>0.1397793051709941</v>
       </c>
       <c r="M5" t="n">
-        <v>2.521223768391743</v>
+        <v>2.552068824352406</v>
       </c>
       <c r="N5" t="n">
-        <v>10.48785266915117</v>
+        <v>10.75595460097049</v>
       </c>
       <c r="O5" t="n">
-        <v>3.238495432936594</v>
+        <v>3.279627204572265</v>
       </c>
       <c r="P5" t="n">
-        <v>382.7038431163685</v>
+        <v>382.7818260035663</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23047,28 +23167,28 @@
         <v>0.1034</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1250629681964508</v>
+        <v>-0.1359591995196133</v>
       </c>
       <c r="J6" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K6" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03481668048988951</v>
+        <v>0.0404132407570601</v>
       </c>
       <c r="M6" t="n">
-        <v>4.254181875100457</v>
+        <v>4.297964836315369</v>
       </c>
       <c r="N6" t="n">
-        <v>26.70714095735381</v>
+        <v>27.19402749954256</v>
       </c>
       <c r="O6" t="n">
-        <v>5.167895215399962</v>
+        <v>5.214789305383541</v>
       </c>
       <c r="P6" t="n">
-        <v>387.4031023583005</v>
+        <v>387.5119481272093</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23125,28 +23245,28 @@
         <v>0.1285</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2341815176607303</v>
+        <v>-0.2413988059698496</v>
       </c>
       <c r="J7" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K7" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0910484588537398</v>
+        <v>0.09647559625241897</v>
       </c>
       <c r="M7" t="n">
-        <v>4.641704104572937</v>
+        <v>4.658918118517533</v>
       </c>
       <c r="N7" t="n">
-        <v>33.72258460234907</v>
+        <v>33.81336689479795</v>
       </c>
       <c r="O7" t="n">
-        <v>5.807114998202556</v>
+        <v>5.814926215765592</v>
       </c>
       <c r="P7" t="n">
-        <v>397.7706885193282</v>
+        <v>397.8427846065976</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23184,7 +23304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H533"/>
+  <dimension ref="A1:H536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45573,6 +45693,132 @@
         </is>
       </c>
     </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>-35.001740267471696,173.7913293796481</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>-35.00191308910362,173.7922059861168</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>-35.00197973185253,173.79309464361418</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>-35.00198483679191,173.79398235902838</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>-35.001878792882486,173.7948557319889</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>-35.00156497722063,173.79564310040814</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>-35.00172830030911,173.7913314045224</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>-35.0019033332855,173.79220743481713</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>-35.00197270888583,173.7930951033645</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>-35.0019846567567,173.79398234635235</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>-35.00188196310721,173.7948565797725</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>-35.00157157429918,173.7956457304877</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>-35.00171704760395,173.7913333085082</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>-35.001895725537416,173.7922085645373</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>-35.001960283637025,173.79309591676872</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>-35.00198159615802,173.79398213085952</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>-35.00187914512968,173.79485582618707</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>-35.00156600533678,173.79564351029066</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0044/nzd0044.xlsx
+++ b/data/nzd0044/nzd0044.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H536"/>
+  <dimension ref="A1:H540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16518,6 +16518,126 @@
         <v>384.57</v>
       </c>
       <c r="H536" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>379.92</v>
+      </c>
+      <c r="C537" t="n">
+        <v>371.28</v>
+      </c>
+      <c r="D537" t="n">
+        <v>372.82</v>
+      </c>
+      <c r="E537" t="n">
+        <v>370.8</v>
+      </c>
+      <c r="F537" t="n">
+        <v>373.18</v>
+      </c>
+      <c r="G537" t="n">
+        <v>385.35</v>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>380.91</v>
+      </c>
+      <c r="C538" t="n">
+        <v>371.98</v>
+      </c>
+      <c r="D538" t="n">
+        <v>373.38</v>
+      </c>
+      <c r="E538" t="n">
+        <v>371.71</v>
+      </c>
+      <c r="F538" t="n">
+        <v>373.03</v>
+      </c>
+      <c r="G538" t="n">
+        <v>383.65</v>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>382.59</v>
+      </c>
+      <c r="C539" t="n">
+        <v>373.2</v>
+      </c>
+      <c r="D539" t="n">
+        <v>374.44</v>
+      </c>
+      <c r="E539" t="n">
+        <v>373.11</v>
+      </c>
+      <c r="F539" t="n">
+        <v>374.31</v>
+      </c>
+      <c r="G539" t="n">
+        <v>384.08</v>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>384.12</v>
+      </c>
+      <c r="C540" t="n">
+        <v>374.22</v>
+      </c>
+      <c r="D540" t="n">
+        <v>374.84</v>
+      </c>
+      <c r="E540" t="n">
+        <v>373.69</v>
+      </c>
+      <c r="F540" t="n">
+        <v>374.64</v>
+      </c>
+      <c r="G540" t="n">
+        <v>383.64</v>
+      </c>
+      <c r="H540" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16534,7 +16654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B615"/>
+  <dimension ref="A1:B619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22687,6 +22807,46 @@
       </c>
       <c r="B615" t="n">
         <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -22855,28 +23015,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06372813896226034</v>
+        <v>-0.06630083730743067</v>
       </c>
       <c r="J2" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="K2" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0128325441592847</v>
+        <v>0.01405042835757486</v>
       </c>
       <c r="M2" t="n">
-        <v>3.537580283525133</v>
+        <v>3.528877147965237</v>
       </c>
       <c r="N2" t="n">
-        <v>19.35692199808771</v>
+        <v>19.2595657532797</v>
       </c>
       <c r="O2" t="n">
-        <v>4.399650213151917</v>
+        <v>4.388572177061658</v>
       </c>
       <c r="P2" t="n">
-        <v>385.5256888077581</v>
+        <v>385.5514832048935</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22933,28 +23093,28 @@
         <v>0.111</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008702094867847086</v>
+        <v>0.005776304097469988</v>
       </c>
       <c r="J3" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="K3" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000311374418986432</v>
+        <v>0.0001389002693488184</v>
       </c>
       <c r="M3" t="n">
-        <v>3.043025551856806</v>
+        <v>3.03806290117782</v>
       </c>
       <c r="N3" t="n">
-        <v>15.06347647405182</v>
+        <v>14.99615804734641</v>
       </c>
       <c r="O3" t="n">
-        <v>3.881169472472417</v>
+        <v>3.872487320488785</v>
       </c>
       <c r="P3" t="n">
-        <v>374.6350769876991</v>
+        <v>374.6644184462832</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23011,28 +23171,28 @@
         <v>0.1222</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09225937960253983</v>
+        <v>-0.09504717876386314</v>
       </c>
       <c r="J4" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="K4" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04757480176365281</v>
+        <v>0.05090712807440123</v>
       </c>
       <c r="M4" t="n">
-        <v>2.691788450878893</v>
+        <v>2.689356569681789</v>
       </c>
       <c r="N4" t="n">
-        <v>10.55773398549565</v>
+        <v>10.51603208271301</v>
       </c>
       <c r="O4" t="n">
-        <v>3.24926668426826</v>
+        <v>3.242843209702407</v>
       </c>
       <c r="P4" t="n">
-        <v>378.4385466268116</v>
+        <v>378.4665071084493</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23089,28 +23249,28 @@
         <v>0.1361</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1679550601337838</v>
+        <v>-0.1758797675792972</v>
       </c>
       <c r="J5" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="K5" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1397793051709941</v>
+        <v>0.1500233754650283</v>
       </c>
       <c r="M5" t="n">
-        <v>2.552068824352406</v>
+        <v>2.580165539757823</v>
       </c>
       <c r="N5" t="n">
-        <v>10.75595460097049</v>
+        <v>10.94266597094712</v>
       </c>
       <c r="O5" t="n">
-        <v>3.279627204572265</v>
+        <v>3.307970068024667</v>
       </c>
       <c r="P5" t="n">
-        <v>382.7818260035663</v>
+        <v>382.861318284654</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23167,28 +23327,28 @@
         <v>0.1034</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1359591995196133</v>
+        <v>-0.1493838465189149</v>
       </c>
       <c r="J6" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="K6" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0404132407570601</v>
+        <v>0.04783751737048625</v>
       </c>
       <c r="M6" t="n">
-        <v>4.297964836315369</v>
+        <v>4.348213335034433</v>
       </c>
       <c r="N6" t="n">
-        <v>27.19402749954256</v>
+        <v>27.73275628871651</v>
       </c>
       <c r="O6" t="n">
-        <v>5.214789305383541</v>
+        <v>5.266189921443823</v>
       </c>
       <c r="P6" t="n">
-        <v>387.5119481272093</v>
+        <v>387.6466225870024</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23245,28 +23405,28 @@
         <v>0.1285</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2413988059698496</v>
+        <v>-0.2509769528407503</v>
       </c>
       <c r="J7" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="K7" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09647559625241897</v>
+        <v>0.1038415755045347</v>
       </c>
       <c r="M7" t="n">
-        <v>4.658918118517533</v>
+        <v>4.681191318020775</v>
       </c>
       <c r="N7" t="n">
-        <v>33.81336689479795</v>
+        <v>33.94099222084363</v>
       </c>
       <c r="O7" t="n">
-        <v>5.814926215765592</v>
+        <v>5.825889822236912</v>
       </c>
       <c r="P7" t="n">
-        <v>397.8427846065976</v>
+        <v>397.9388813908228</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23304,7 +23464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H536"/>
+  <dimension ref="A1:H540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45819,6 +45979,174 @@
         </is>
       </c>
     </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>-35.00171034956514,173.79133444183282</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>-35.001892413929404,173.79220905629782</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>-35.00195875299043,173.7930960169707</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>-35.001983036439746,173.79398223226792</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>-35.00188117055104,173.79485636782658</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>-35.001559322581834,173.7956408460546</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>-35.00170150815388,173.79133593782106</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>-35.00188614872507,173.7922099866554</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>-35.0019537108605,173.7930963470477</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>-35.00197484483736,173.7939816555078</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>-35.00188249147801,173.79485672106978</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>-35.001573887560475,173.7956466527235</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>-35.001686504546846,173.7913384764671</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>-35.001875229368906,173.7922116081355</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>-35.00194416682878,173.79309697183626</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>-35.00196224237211,173.79398076818475</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>-35.00187121956783,173.79485370672833</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>-35.001570203477684,173.79564518397763</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>-35.00167284054751,173.79134078844754</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>-35.001866100071126,173.79221296379882</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>-35.00194056530737,173.79309720760548</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>-35.00195702135079,173.7939804005796</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>-35.001868313528476,173.7948529295936</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>-35.00157397323683,173.79564668688036</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
